--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,733 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122387568</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98175</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590107</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6441133</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122387532</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590142</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6441088</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122386698</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90212</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590132</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6441124</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122387576</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590107</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6441133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122385420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97371</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590121</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6441113</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122387556</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590128</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6441123</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387568</v>
+        <v>122387532</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590107</v>
+        <v>590142</v>
       </c>
       <c r="R3" t="n">
-        <v>6441133</v>
+        <v>6441088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387532</v>
+        <v>122387556</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,34 +924,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590142</v>
+        <v>590128</v>
       </c>
       <c r="R4" t="n">
-        <v>6441088</v>
+        <v>6441123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,13 +1008,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386698</v>
+        <v>122387576</v>
       </c>
       <c r="B5" t="n">
-        <v>90212</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,45 +1053,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2008</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590132</v>
+        <v>590107</v>
       </c>
       <c r="R5" t="n">
-        <v>6441124</v>
+        <v>6441133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,14 +1118,24 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Spår, födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,29 +1144,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387576</v>
+        <v>122385420</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>97381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,49 +1174,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590107</v>
+        <v>590121</v>
       </c>
       <c r="R6" t="n">
-        <v>6441133</v>
+        <v>6441113</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,54 +1247,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122385420</v>
+        <v>122386698</v>
       </c>
       <c r="B7" t="n">
-        <v>97371</v>
+        <v>90222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,39 +1289,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>569</v>
+        <v>2008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,13 +1328,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590121</v>
+        <v>590132</v>
       </c>
       <c r="R7" t="n">
-        <v>6441113</v>
+        <v>6441124</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,6 +1364,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387556</v>
+        <v>122387568</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,35 +1408,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1440,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590128</v>
+        <v>590107</v>
       </c>
       <c r="R8" t="n">
-        <v>6441123</v>
+        <v>6441133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,17 +1492,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387532</v>
+        <v>122386698</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,47 +802,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590142</v>
+        <v>590132</v>
       </c>
       <c r="R3" t="n">
-        <v>6441088</v>
+        <v>6441124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +874,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1037,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387576</v>
+        <v>122387568</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,35 +1046,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1133,17 +1130,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1277,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386698</v>
+        <v>122387532</v>
       </c>
       <c r="B7" t="n">
-        <v>90222</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,49 +1282,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2008</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590132</v>
+        <v>590142</v>
       </c>
       <c r="R7" t="n">
-        <v>6441124</v>
+        <v>6441088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,14 +1352,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,35 +1404,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1492,13 +1488,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122363011</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>122386698</v>
       </c>
       <c r="B3" t="n">
-        <v>90222</v>
+        <v>90234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387556</v>
+        <v>122387568</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +921,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590128</v>
+        <v>590107</v>
       </c>
       <c r="R4" t="n">
-        <v>6441123</v>
+        <v>6441133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,17 +1005,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,35 +1042,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,13 +1126,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>122385420</v>
       </c>
       <c r="B6" t="n">
-        <v>97381</v>
+        <v>97393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387576</v>
+        <v>122387556</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R8" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386698</v>
+        <v>122387576</v>
       </c>
       <c r="B3" t="n">
-        <v>90234</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,45 +806,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590132</v>
+        <v>590107</v>
       </c>
       <c r="R3" t="n">
-        <v>6441124</v>
+        <v>6441133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,14 +871,24 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Spår, födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,29 +897,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387568</v>
+        <v>122387532</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +927,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590107</v>
+        <v>590142</v>
       </c>
       <c r="R4" t="n">
-        <v>6441133</v>
+        <v>6441088</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387576</v>
+        <v>122387568</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1049,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1126,17 +1133,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1155,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385420</v>
+        <v>122386698</v>
       </c>
       <c r="B6" t="n">
-        <v>97393</v>
+        <v>90238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1170,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>569</v>
+        <v>2008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590121</v>
+        <v>590132</v>
       </c>
       <c r="R6" t="n">
-        <v>6441113</v>
+        <v>6441124</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,6 +1245,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387532</v>
+        <v>122385420</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>97398</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,46 +1293,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590142</v>
+        <v>590121</v>
       </c>
       <c r="R7" t="n">
-        <v>6441088</v>
+        <v>6441113</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,19 +1362,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,12 +1380,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -783,14 +778,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387576</v>
+        <v>122387556</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -807,11 +802,6 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R3" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -915,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387532</v>
+        <v>122385420</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>97407</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,46 +921,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>569</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590142</v>
+        <v>590121</v>
       </c>
       <c r="R4" t="n">
-        <v>6441088</v>
+        <v>6441113</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,19 +985,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387568</v>
+        <v>122386698</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>90243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,46 +1027,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>2008</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590107</v>
+        <v>590132</v>
       </c>
       <c r="R5" t="n">
-        <v>6441133</v>
+        <v>6441124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,19 +1094,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,22 +1117,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386698</v>
+        <v>122387576</v>
       </c>
       <c r="B6" t="n">
-        <v>90238</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,45 +1145,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fyrflikig jordstjärna</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590132</v>
+        <v>590107</v>
       </c>
       <c r="R6" t="n">
-        <v>6441124</v>
+        <v>6441133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,14 +1205,24 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Spår, födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,29 +1231,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122385420</v>
+        <v>122387532</v>
       </c>
       <c r="B7" t="n">
-        <v>97398</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,49 +1265,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>569</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590121</v>
+        <v>590142</v>
       </c>
       <c r="R7" t="n">
-        <v>6441113</v>
+        <v>6441088</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,9 +1326,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387556</v>
+        <v>122387568</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,35 +1378,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1440,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590128</v>
+        <v>590107</v>
       </c>
       <c r="R8" t="n">
-        <v>6441123</v>
+        <v>6441133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,17 +1457,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122363011</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387556</v>
+        <v>122387532</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,28 +802,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590128</v>
+        <v>590142</v>
       </c>
       <c r="R3" t="n">
-        <v>6441123</v>
+        <v>6441088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +887,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122385420</v>
+        <v>122387576</v>
       </c>
       <c r="B4" t="n">
-        <v>97407</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,48 +924,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590121</v>
+        <v>590107</v>
       </c>
       <c r="R4" t="n">
-        <v>6441113</v>
+        <v>6441133</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,30 +993,44 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1018,7 +1040,7 @@
         <v>122386698</v>
       </c>
       <c r="B5" t="n">
-        <v>90243</v>
+        <v>90256</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,6 +1054,11 @@
       </c>
       <c r="E5" t="n">
         <v>2008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1129,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387576</v>
+        <v>122387556</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,6 +1173,11 @@
       </c>
       <c r="E6" t="n">
         <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1172,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R6" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387532</v>
+        <v>122385420</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>97420</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,41 +1297,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590142</v>
+        <v>590121</v>
       </c>
       <c r="R7" t="n">
-        <v>6441088</v>
+        <v>6441113</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,19 +1366,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1384,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1369,7 +1399,7 @@
         <v>122387568</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,6 +1413,11 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387532</v>
+        <v>122386698</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,47 +802,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590142</v>
+        <v>590132</v>
       </c>
       <c r="R3" t="n">
-        <v>6441088</v>
+        <v>6441124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +874,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387576</v>
+        <v>122385420</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>97433</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,49 +921,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590107</v>
+        <v>590121</v>
       </c>
       <c r="R4" t="n">
-        <v>6441133</v>
+        <v>6441113</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,54 +994,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122386698</v>
+        <v>122387532</v>
       </c>
       <c r="B5" t="n">
-        <v>90256</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,49 +1036,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2008</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590132</v>
+        <v>590142</v>
       </c>
       <c r="R5" t="n">
-        <v>6441124</v>
+        <v>6441088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,14 +1106,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,12 +1134,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1281,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122385420</v>
+        <v>122387568</v>
       </c>
       <c r="B7" t="n">
-        <v>97420</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,32 +1283,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>569</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1329,17 +1315,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590121</v>
+        <v>590107</v>
       </c>
       <c r="R7" t="n">
-        <v>6441113</v>
+        <v>6441133</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,9 +1352,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,7 +1380,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1396,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,35 +1404,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1492,13 +1488,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386698</v>
+        <v>122387568</v>
       </c>
       <c r="B3" t="n">
-        <v>90269</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,49 +802,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590132</v>
+        <v>590107</v>
       </c>
       <c r="R3" t="n">
-        <v>6441124</v>
+        <v>6441133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,14 +871,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +899,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122385420</v>
+        <v>122387532</v>
       </c>
       <c r="B4" t="n">
-        <v>97433</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,49 +927,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590121</v>
+        <v>590142</v>
       </c>
       <c r="R4" t="n">
-        <v>6441113</v>
+        <v>6441088</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,9 +993,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,22 +1021,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387532</v>
+        <v>122385420</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>97433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,46 +1049,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590142</v>
+        <v>590121</v>
       </c>
       <c r="R5" t="n">
-        <v>6441088</v>
+        <v>6441113</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,19 +1118,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387556</v>
+        <v>122386698</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>90269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,42 +1164,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590128</v>
+        <v>590132</v>
       </c>
       <c r="R6" t="n">
-        <v>6441123</v>
+        <v>6441124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,24 +1232,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spår, födosök</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,28 +1248,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1279,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1367,13 +1363,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387576</v>
+        <v>122387556</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R8" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387568</v>
+        <v>122387532</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590107</v>
+        <v>590142</v>
       </c>
       <c r="R3" t="n">
-        <v>6441133</v>
+        <v>6441088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387532</v>
+        <v>122387576</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,34 +924,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590142</v>
+        <v>590107</v>
       </c>
       <c r="R4" t="n">
-        <v>6441088</v>
+        <v>6441133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,13 +1008,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,7 +1040,7 @@
         <v>122385420</v>
       </c>
       <c r="B5" t="n">
-        <v>97433</v>
+        <v>97436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1267,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387576</v>
+        <v>122387568</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,35 +1283,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1363,17 +1367,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387532</v>
+        <v>122386698</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,47 +802,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590142</v>
+        <v>590132</v>
       </c>
       <c r="R3" t="n">
-        <v>6441088</v>
+        <v>6441124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +874,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387576</v>
+        <v>122387568</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,35 +921,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1008,17 +1005,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122385420</v>
+        <v>122387556</v>
       </c>
       <c r="B5" t="n">
-        <v>97436</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,53 +1042,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590121</v>
+        <v>590128</v>
       </c>
       <c r="R5" t="n">
-        <v>6441113</v>
+        <v>6441123</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,25 +1111,39 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1152,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386698</v>
+        <v>122385420</v>
       </c>
       <c r="B6" t="n">
-        <v>90269</v>
+        <v>97436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,38 +1167,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590132</v>
+        <v>590121</v>
       </c>
       <c r="R6" t="n">
-        <v>6441124</v>
+        <v>6441113</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,11 +1243,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387568</v>
+        <v>122387532</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1282,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590107</v>
+        <v>590142</v>
       </c>
       <c r="R7" t="n">
-        <v>6441133</v>
+        <v>6441088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387556</v>
+        <v>122387576</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590128</v>
+        <v>590107</v>
       </c>
       <c r="R8" t="n">
-        <v>6441123</v>
+        <v>6441133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122363011</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122386698</v>
+        <v>122385420</v>
       </c>
       <c r="B3" t="n">
-        <v>90269</v>
+        <v>97437</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590132</v>
+        <v>590121</v>
       </c>
       <c r="R3" t="n">
-        <v>6441124</v>
+        <v>6441113</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1005,13 +1001,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>122387556</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385420</v>
+        <v>122386698</v>
       </c>
       <c r="B6" t="n">
-        <v>97436</v>
+        <v>90270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1167,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>569</v>
+        <v>2008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590121</v>
+        <v>590132</v>
       </c>
       <c r="R6" t="n">
-        <v>6441113</v>
+        <v>6441124</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,6 +1242,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1392,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387576</v>
+        <v>122387568</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,35 +1408,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1488,17 +1492,13 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122385420</v>
+        <v>122387568</v>
       </c>
       <c r="B3" t="n">
-        <v>97437</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,32 +802,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -838,17 +834,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590121</v>
+        <v>590107</v>
       </c>
       <c r="R3" t="n">
-        <v>6441113</v>
+        <v>6441133</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,9 +871,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,12 +899,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387556</v>
+        <v>122385420</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>97440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,49 +1048,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590128</v>
+        <v>590121</v>
       </c>
       <c r="R5" t="n">
-        <v>6441123</v>
+        <v>6441113</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,39 +1121,25 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1155,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122386698</v>
+        <v>122387532</v>
       </c>
       <c r="B6" t="n">
-        <v>90270</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,49 +1163,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590132</v>
+        <v>590142</v>
       </c>
       <c r="R6" t="n">
-        <v>6441124</v>
+        <v>6441088</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,14 +1233,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387532</v>
+        <v>122386698</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>90273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,47 +1285,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590142</v>
+        <v>590132</v>
       </c>
       <c r="R7" t="n">
-        <v>6441088</v>
+        <v>6441124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,19 +1357,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387568</v>
+        <v>122387556</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,35 +1404,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1444,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R8" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,13 +1488,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387568</v>
+        <v>122387576</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -886,13 +886,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387576</v>
+        <v>122387556</v>
       </c>
       <c r="B4" t="n">
         <v>57400</v>
@@ -959,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590107</v>
+        <v>590128</v>
       </c>
       <c r="R4" t="n">
-        <v>6441133</v>
+        <v>6441123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122385420</v>
+        <v>122387568</v>
       </c>
       <c r="B5" t="n">
-        <v>97440</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,32 +1052,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>569</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1084,17 +1084,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590121</v>
+        <v>590107</v>
       </c>
       <c r="R5" t="n">
-        <v>6441113</v>
+        <v>6441133</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,9 +1121,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1149,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1151,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387532</v>
+        <v>122385420</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>97440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,46 +1177,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590142</v>
+        <v>590121</v>
       </c>
       <c r="R6" t="n">
-        <v>6441088</v>
+        <v>6441113</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,19 +1246,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,22 +1264,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122386698</v>
+        <v>122387532</v>
       </c>
       <c r="B7" t="n">
-        <v>90273</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,49 +1288,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2008</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590132</v>
+        <v>590142</v>
       </c>
       <c r="R7" t="n">
-        <v>6441124</v>
+        <v>6441088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,14 +1358,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,22 +1386,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387556</v>
+        <v>122386698</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
+        <v>90273</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,42 +1414,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590128</v>
+        <v>590132</v>
       </c>
       <c r="R8" t="n">
-        <v>6441123</v>
+        <v>6441124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,24 +1482,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spår, födosök</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,18 +1498,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">

--- a/artfynd/A 1779-2025 artfynd.xlsx
+++ b/artfynd/A 1779-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363011</v>
+        <v>122385241</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590152</v>
+        <v>590097</v>
       </c>
       <c r="R2" t="n">
-        <v>6441108</v>
+        <v>6441248</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,79 +766,79 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387576</v>
+        <v>122385420</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590107</v>
+        <v>590121</v>
       </c>
       <c r="R3" t="n">
-        <v>6441133</v>
+        <v>6441113</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,59 +865,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår, födosök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387556</v>
+        <v>122386698</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,42 +906,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590128</v>
+        <v>590132</v>
       </c>
       <c r="R4" t="n">
-        <v>6441123</v>
+        <v>6441124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,24 +974,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår, födosök</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,76 +990,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387568</v>
+        <v>122363011</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1767, Svartgöl, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590107</v>
+        <v>590152</v>
       </c>
       <c r="R5" t="n">
-        <v>6441133</v>
+        <v>6441108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,22 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1101,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385420</v>
+        <v>122387556</v>
       </c>
       <c r="B6" t="n">
-        <v>97440</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,49 +1130,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590121</v>
+        <v>590128</v>
       </c>
       <c r="R6" t="n">
-        <v>6441113</v>
+        <v>6441123</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,45 +1195,54 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387532</v>
+        <v>122387576</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,30 +1250,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1325,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590142</v>
+        <v>590107</v>
       </c>
       <c r="R7" t="n">
-        <v>6441088</v>
+        <v>6441133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,13 +1330,17 @@
           <t>09:45</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår, födosök</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1398,61 +1359,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122386698</v>
+        <v>122387532</v>
       </c>
       <c r="B8" t="n">
-        <v>90273</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2008</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 1767, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590132</v>
+        <v>590142</v>
       </c>
       <c r="R8" t="n">
-        <v>6441124</v>
+        <v>6441088</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,21 +1436,26 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1505,15 +1464,693 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122387614</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 2806, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590099</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6441240</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122387610</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 2806, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6441240</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122362994</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 1779, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590215</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6441152</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122387568</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590107</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6441133</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122387641</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 2806, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590098</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6441232</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122435344</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 2806, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590106</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6441250</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
